--- a/data/trans_camb/IP43-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP43-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 11,55</t>
+          <t>-9,36; 11,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,9; -7,93</t>
+          <t>-24,06; -8,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 4,51</t>
+          <t>-18,61; 5,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,25; -15,65</t>
+          <t>-33,78; -15,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 5,34</t>
+          <t>-11,9; 4,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,74; -14,15</t>
+          <t>-26,0; -14,14</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,93; 128,09</t>
+          <t>-51,42; 125,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 27,88</t>
+          <t>-63,21; 39,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,9; 40,9</t>
+          <t>-48,18; 32,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,15; -8,8</t>
+          <t>-19,38; -8,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -8,63</t>
+          <t>-19,49; -8,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,31; -14,02</t>
+          <t>-26,91; -13,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,98; -14,35</t>
+          <t>-27,47; -14,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -12,84</t>
+          <t>-21,2; -13,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,96; -13,14</t>
+          <t>-21,66; -13,51</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -82,34</t>
+          <t>-100,0; -84,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -89,57</t>
+          <t>-100,0; -92,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 0,0</t>
+          <t>-5,58; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 0,0</t>
+          <t>-6,02; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 6,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,05</t>
+          <t>-1,67; 1,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,0</t>
+          <t>-3,47; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 13,92</t>
+          <t>-4,14; 14,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,7; -6,85</t>
+          <t>-19,15; -6,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 4,89</t>
+          <t>-9,61; 4,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,1; -4,14</t>
+          <t>-15,19; -3,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 7,48</t>
+          <t>-4,73; 6,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -6,59</t>
+          <t>-15,3; -6,55</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 185,5</t>
+          <t>-28,26; 190,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,44; 136,03</t>
+          <t>-78,34; 95,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 112,61</t>
+          <t>-37,07; 86,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-61,11; -28,57</t>
+          <t>-60,65; -28,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-89,84; -70,06</t>
+          <t>-89,85; -68,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-63,65; -34,27</t>
+          <t>-63,04; -32,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-88,13; -67,99</t>
+          <t>-87,15; -66,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-58,33; -37,69</t>
+          <t>-59,24; -37,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-86,2; -72,71</t>
+          <t>-86,19; -72,03</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,74; -38,98</t>
+          <t>-71,54; -39,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-76,67; -46,34</t>
+          <t>-75,17; -45,94</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-70,59; -49,34</t>
+          <t>-71,24; -49,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 6,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,64; 11,75</t>
+          <t>0,46; 11,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,0</t>
+          <t>-4,1; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,57</t>
+          <t>0,62; 7,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-1,84; 0,0</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 1,76</t>
+          <t>-5,43; 1,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,68; -1,93</t>
+          <t>-7,9; -1,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 2,61</t>
+          <t>-5,41; 2,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -2,28</t>
+          <t>-8,31; -2,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,88</t>
+          <t>-4,33; 1,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -2,67</t>
+          <t>-6,66; -2,79</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-89,4; 142,69</t>
+          <t>-88,71; 110,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-79,75; 103,37</t>
+          <t>-77,79; 125,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 34,84</t>
+          <t>-75,36; 39,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-33,41; -17,72</t>
+          <t>-33,37; -17,21</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-59,41; -47,04</t>
+          <t>-60,08; -47,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-31,24; -15,72</t>
+          <t>-31,99; -15,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-57,41; -44,6</t>
+          <t>-57,4; -45,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-30,4; -18,95</t>
+          <t>-30,63; -18,18</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-57,33; -48,05</t>
+          <t>-56,99; -48,26</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-58,26; -36,1</t>
+          <t>-58,04; -34,05</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-57,07; -33,5</t>
+          <t>-57,98; -32,98</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-54,78; -38,56</t>
+          <t>-55,16; -37,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -7,09</t>
+          <t>-14,03; -7,35</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-25,82; -20,59</t>
+          <t>-25,51; -20,6</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -8,97</t>
+          <t>-15,34; -8,64</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-26,06; -20,77</t>
+          <t>-25,83; -20,87</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -8,86</t>
+          <t>-13,29; -8,84</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -21,13</t>
+          <t>-24,95; -21,47</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -34,58</t>
+          <t>-56,01; -34,47</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-59,6; -41,59</t>
+          <t>-60,1; -40,06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-55,23; -40,91</t>
+          <t>-55,25; -40,38</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
